--- a/Data/Home/BedroomOne.Curtain001.xlsx
+++ b/Data/Home/BedroomOne.Curtain001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709428729</v>
+        <v>1712116202</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709460804</v>
+        <v>1712147220</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709688465</v>
+        <v>1712466919</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709719214</v>
+        <v>1712508648</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1710034243</v>
+        <v>1713153809</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1710056825</v>
+        <v>1713174100</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1710380270</v>
+        <v>1713843989</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1710408194</v>
+        <v>1713872761</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1710551622</v>
+        <v>1714017363</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1710576893</v>
+        <v>1714040827</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,150 +843,7 @@
           <t>physical</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1710726801</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>BedroomOne.Curtain001.state: open</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1710754618</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>BedroomOne.Curtain001.state: close</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1710987967</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BedroomOne.Curtain001.state: open</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1711015793</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BedroomOne.Curtain001.state: close</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
